--- a/Team-Data/2011-12/4-25-2011-12.xlsx
+++ b/Team-Data/2011-12/4-25-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,13 +806,13 @@
         <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>9</v>
       </c>
       <c r="AF2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
         <v>9</v>
@@ -775,7 +842,7 @@
         <v>22</v>
       </c>
       <c r="AP2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ2" t="n">
         <v>23</v>
@@ -793,7 +860,7 @@
         <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW2" t="n">
         <v>10</v>
@@ -802,7 +869,7 @@
         <v>23</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
         <v>6</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>2.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>10</v>
@@ -933,7 +1000,7 @@
         <v>10</v>
       </c>
       <c r="AH3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI3" t="n">
         <v>23</v>
@@ -951,7 +1018,7 @@
         <v>24</v>
       </c>
       <c r="AN3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO3" t="n">
         <v>24</v>
@@ -978,7 +1045,7 @@
         <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX3" t="n">
         <v>7</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -1025,52 +1092,52 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G4" t="n">
-        <v>0.108</v>
+        <v>0.109</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
       </c>
       <c r="I4" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="J4" t="n">
-        <v>80.3</v>
+        <v>80.5</v>
       </c>
       <c r="K4" t="n">
         <v>0.414</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="M4" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="N4" t="n">
         <v>0.293</v>
       </c>
       <c r="O4" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="P4" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.749</v>
+        <v>0.746</v>
       </c>
       <c r="R4" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S4" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="T4" t="n">
         <v>39</v>
@@ -1082,28 +1149,28 @@
         <v>14.5</v>
       </c>
       <c r="W4" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="X4" t="n">
         <v>5.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>87</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-13.8</v>
+        <v>-13.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1121,7 +1188,7 @@
         <v>30</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
         <v>30</v>
@@ -1136,7 +1203,7 @@
         <v>30</v>
       </c>
       <c r="AO4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP4" t="n">
         <v>15</v>
@@ -1154,22 +1221,22 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
         <v>29</v>
       </c>
       <c r="AX4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
         <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.754</v>
+        <v>0.75</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
@@ -1225,7 +1292,7 @@
         <v>37.3</v>
       </c>
       <c r="J5" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K5" t="n">
         <v>0.45</v>
@@ -1240,19 +1307,19 @@
         <v>0.376</v>
       </c>
       <c r="O5" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="P5" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.722</v>
+        <v>0.72</v>
       </c>
       <c r="R5" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="S5" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T5" t="n">
         <v>46.5</v>
@@ -1264,28 +1331,28 @@
         <v>14.1</v>
       </c>
       <c r="W5" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X5" t="n">
         <v>5.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z5" t="n">
         <v>17.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.2</v>
+        <v>96.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1300,13 +1367,13 @@
         <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ5" t="n">
         <v>7</v>
       </c>
       <c r="AK5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL5" t="n">
         <v>17</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E6" t="n">
         <v>21</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>0.323</v>
+        <v>0.328</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
@@ -1407,31 +1474,31 @@
         <v>34.4</v>
       </c>
       <c r="J6" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K6" t="n">
         <v>0.423</v>
       </c>
       <c r="L6" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M6" t="n">
         <v>19.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O6" t="n">
         <v>17.9</v>
       </c>
       <c r="P6" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
         <v>0.717</v>
       </c>
       <c r="R6" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S6" t="n">
         <v>29.6</v>
@@ -1455,25 +1522,25 @@
         <v>6.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA6" t="n">
         <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>-6.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
         <v>26</v>
       </c>
       <c r="AF6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG6" t="n">
         <v>26</v>
@@ -1497,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
         <v>9</v>
@@ -1515,7 +1582,7 @@
         <v>22</v>
       </c>
       <c r="AT6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU6" t="n">
         <v>21</v>
@@ -1533,13 +1600,13 @@
         <v>28</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA6" t="n">
         <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>1.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AF7" t="n">
         <v>13</v>
@@ -1694,7 +1761,7 @@
         <v>27</v>
       </c>
       <c r="AS7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT7" t="n">
         <v>9</v>
@@ -1715,7 +1782,7 @@
         <v>1</v>
       </c>
       <c r="AZ7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8" t="n">
         <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>0.569</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H8" t="n">
         <v>48.6</v>
@@ -1771,10 +1838,10 @@
         <v>38.7</v>
       </c>
       <c r="J8" t="n">
-        <v>81.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="L8" t="n">
         <v>6.6</v>
@@ -1783,22 +1850,22 @@
         <v>20</v>
       </c>
       <c r="N8" t="n">
-        <v>0.331</v>
+        <v>0.33</v>
       </c>
       <c r="O8" t="n">
         <v>19.7</v>
       </c>
       <c r="P8" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.735</v>
+        <v>0.737</v>
       </c>
       <c r="R8" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S8" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T8" t="n">
         <v>43</v>
@@ -1816,7 +1883,7 @@
         <v>5</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="Z8" t="n">
         <v>19.6</v>
@@ -1828,10 +1895,10 @@
         <v>103.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR8" t="n">
         <v>18</v>
@@ -1879,7 +1946,7 @@
         <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
@@ -1891,7 +1958,7 @@
         <v>9</v>
       </c>
       <c r="AX8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY8" t="n">
         <v>30</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-5.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>22</v>
@@ -2025,7 +2092,7 @@
         <v>22</v>
       </c>
       <c r="AH9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI9" t="n">
         <v>25</v>
@@ -2043,10 +2110,10 @@
         <v>26</v>
       </c>
       <c r="AN9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP9" t="n">
         <v>14</v>
@@ -2055,7 +2122,7 @@
         <v>18</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
         <v>30</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,13 +2274,13 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
         <v>7</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK10" t="n">
         <v>9</v>
@@ -2240,7 +2307,7 @@
         <v>29</v>
       </c>
       <c r="AS10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT10" t="n">
         <v>28</v>
@@ -2249,7 +2316,7 @@
         <v>9</v>
       </c>
       <c r="AV10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW10" t="n">
         <v>11</v>
@@ -2258,7 +2325,7 @@
         <v>6</v>
       </c>
       <c r="AY10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ10" t="n">
         <v>27</v>
@@ -2267,7 +2334,7 @@
         <v>29</v>
       </c>
       <c r="BB10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC10" t="n">
         <v>22</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>0.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>17</v>
@@ -2392,7 +2459,7 @@
         <v>3</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ11" t="n">
         <v>3</v>
@@ -2449,7 +2516,7 @@
         <v>25</v>
       </c>
       <c r="BB11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
         <v>18</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E12" t="n">
         <v>42</v>
       </c>
       <c r="F12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G12" t="n">
-        <v>0.636</v>
+        <v>0.646</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
@@ -2499,7 +2566,7 @@
         <v>35.7</v>
       </c>
       <c r="J12" t="n">
-        <v>81.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="K12" t="n">
         <v>0.438</v>
@@ -2508,34 +2575,34 @@
         <v>5.9</v>
       </c>
       <c r="M12" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="N12" t="n">
         <v>0.368</v>
       </c>
       <c r="O12" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="P12" t="n">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.782</v>
+        <v>0.783</v>
       </c>
       <c r="R12" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S12" t="n">
         <v>31.4</v>
       </c>
       <c r="T12" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="U12" t="n">
         <v>18.6</v>
       </c>
       <c r="V12" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W12" t="n">
         <v>7.9</v>
@@ -2547,16 +2614,16 @@
         <v>6</v>
       </c>
       <c r="Z12" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AA12" t="n">
         <v>21.7</v>
       </c>
-      <c r="AA12" t="n">
-        <v>21.6</v>
-      </c>
       <c r="AB12" t="n">
-        <v>97.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
@@ -2577,7 +2644,7 @@
         <v>21</v>
       </c>
       <c r="AJ12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK12" t="n">
         <v>24</v>
@@ -2589,7 +2656,7 @@
         <v>22</v>
       </c>
       <c r="AN12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
@@ -2607,19 +2674,19 @@
         <v>9</v>
       </c>
       <c r="AT12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU12" t="n">
         <v>28</v>
       </c>
       <c r="AV12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW12" t="n">
         <v>14</v>
       </c>
       <c r="AX12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY12" t="n">
         <v>27</v>
@@ -2631,7 +2698,7 @@
         <v>4</v>
       </c>
       <c r="BB12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BC12" t="n">
         <v>6</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E13" t="n">
         <v>40</v>
       </c>
       <c r="F13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>0.606</v>
+        <v>0.615</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2681,31 +2748,31 @@
         <v>37</v>
       </c>
       <c r="J13" t="n">
-        <v>81.3</v>
+        <v>81.5</v>
       </c>
       <c r="K13" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M13" t="n">
         <v>21.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O13" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="P13" t="n">
         <v>23.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.68</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S13" t="n">
         <v>29.4</v>
@@ -2720,7 +2787,7 @@
         <v>13.3</v>
       </c>
       <c r="W13" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X13" t="n">
         <v>4.8</v>
@@ -2732,13 +2799,13 @@
         <v>21.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AD13" t="n">
         <v>1</v>
@@ -2747,19 +2814,19 @@
         <v>7</v>
       </c>
       <c r="AF13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH13" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AI13" t="n">
         <v>13</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK13" t="n">
         <v>10</v>
@@ -2777,19 +2844,19 @@
         <v>21</v>
       </c>
       <c r="AP13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ13" t="n">
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AS13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU13" t="n">
         <v>13</v>
@@ -2801,7 +2868,7 @@
         <v>6</v>
       </c>
       <c r="AX13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY13" t="n">
         <v>6</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -2923,13 +2990,13 @@
         <v>1.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
       </c>
       <c r="AF14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG14" t="n">
         <v>6</v>
@@ -2941,7 +3008,7 @@
         <v>15</v>
       </c>
       <c r="AJ14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK14" t="n">
         <v>7</v>
@@ -2965,7 +3032,7 @@
         <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>1.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>7</v>
@@ -3117,7 +3184,7 @@
         <v>7</v>
       </c>
       <c r="AH15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI15" t="n">
         <v>14</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -3287,19 +3354,19 @@
         <v>6.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
       </c>
       <c r="AF16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG16" t="n">
         <v>4</v>
       </c>
       <c r="AH16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI16" t="n">
         <v>11</v>
@@ -3308,7 +3375,7 @@
         <v>26</v>
       </c>
       <c r="AK16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL16" t="n">
         <v>20</v>
@@ -3338,7 +3405,7 @@
         <v>18</v>
       </c>
       <c r="AU16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV16" t="n">
         <v>19</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -3391,22 +3458,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E17" t="n">
         <v>31</v>
       </c>
       <c r="F17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G17" t="n">
-        <v>0.477</v>
+        <v>0.484</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
       </c>
       <c r="I17" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J17" t="n">
         <v>85.8</v>
@@ -3418,58 +3485,58 @@
         <v>6.7</v>
       </c>
       <c r="M17" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0.346</v>
+        <v>0.345</v>
       </c>
       <c r="O17" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="P17" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="Q17" t="n">
         <v>0.777</v>
       </c>
       <c r="R17" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S17" t="n">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="T17" t="n">
-        <v>42.4</v>
+        <v>42.2</v>
       </c>
       <c r="U17" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V17" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W17" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.40000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3502,10 +3569,10 @@
         <v>15</v>
       </c>
       <c r="AO17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ17" t="n">
         <v>7</v>
@@ -3514,22 +3581,22 @@
         <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU17" t="n">
         <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW17" t="n">
         <v>7</v>
       </c>
       <c r="AX17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY17" t="n">
         <v>5</v>
@@ -3538,7 +3605,7 @@
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
         <v>21</v>
@@ -3663,7 +3730,7 @@
         <v>21</v>
       </c>
       <c r="AH18" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI18" t="n">
         <v>22</v>
@@ -3675,7 +3742,7 @@
         <v>27</v>
       </c>
       <c r="AL18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM18" t="n">
         <v>6</v>
@@ -3693,13 +3760,13 @@
         <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
         <v>8</v>
       </c>
       <c r="AT18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU18" t="n">
         <v>25</v>
@@ -3711,10 +3778,10 @@
         <v>26</v>
       </c>
       <c r="AX18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY18" t="n">
         <v>24</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>25</v>
       </c>
       <c r="AZ18" t="n">
         <v>7</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-5.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
         <v>24</v>
@@ -3845,7 +3912,7 @@
         <v>24</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI19" t="n">
         <v>27</v>
@@ -3863,7 +3930,7 @@
         <v>3</v>
       </c>
       <c r="AN19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO19" t="n">
         <v>13</v>
@@ -3890,25 +3957,25 @@
         <v>19</v>
       </c>
       <c r="AW19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX19" t="n">
         <v>30</v>
       </c>
       <c r="AY19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ19" t="n">
         <v>12</v>
       </c>
       <c r="BA19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB19" t="n">
         <v>23</v>
       </c>
       <c r="BC19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -4015,19 +4082,19 @@
         <v>-3.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE20" t="n">
         <v>26</v>
       </c>
       <c r="AF20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4051,7 +4118,7 @@
         <v>20</v>
       </c>
       <c r="AP20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ20" t="n">
         <v>13</v>
@@ -4075,13 +4142,13 @@
         <v>21</v>
       </c>
       <c r="AX20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA20" t="n">
         <v>23</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E21" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F21" t="n">
         <v>30</v>
       </c>
       <c r="G21" t="n">
-        <v>0.538</v>
+        <v>0.531</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4146,7 +4213,7 @@
         <v>7.8</v>
       </c>
       <c r="M21" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="N21" t="n">
         <v>0.335</v>
@@ -4161,19 +4228,19 @@
         <v>0.743</v>
       </c>
       <c r="R21" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S21" t="n">
         <v>30.5</v>
       </c>
       <c r="T21" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U21" t="n">
         <v>20</v>
       </c>
       <c r="V21" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="W21" t="n">
         <v>9.5</v>
@@ -4191,22 +4258,22 @@
         <v>21.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.8</v>
+        <v>97.7</v>
       </c>
       <c r="AC21" t="n">
         <v>2.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF21" t="n">
         <v>14</v>
       </c>
       <c r="AG21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH21" t="n">
         <v>16</v>
@@ -4218,7 +4285,7 @@
         <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="n">
         <v>4</v>
@@ -4233,7 +4300,7 @@
         <v>7</v>
       </c>
       <c r="AP21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ21" t="n">
         <v>21</v>
@@ -4260,7 +4327,7 @@
         <v>27</v>
       </c>
       <c r="AY21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ21" t="n">
         <v>24</v>
@@ -4269,7 +4336,7 @@
         <v>2</v>
       </c>
       <c r="BB21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC21" t="n">
         <v>8</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E22" t="n">
         <v>47</v>
       </c>
       <c r="F22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G22" t="n">
-        <v>0.712</v>
+        <v>0.723</v>
       </c>
       <c r="H22" t="n">
         <v>48.5</v>
@@ -4322,22 +4389,22 @@
         <v>79.2</v>
       </c>
       <c r="K22" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="L22" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M22" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="O22" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="P22" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="Q22" t="n">
         <v>0.806</v>
@@ -4346,28 +4413,28 @@
         <v>11</v>
       </c>
       <c r="S22" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T22" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="U22" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="V22" t="n">
         <v>16.3</v>
       </c>
       <c r="W22" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="Y22" t="n">
         <v>4.9</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA22" t="n">
         <v>20</v>
@@ -4376,7 +4443,7 @@
         <v>103.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
@@ -4400,10 +4467,10 @@
         <v>25</v>
       </c>
       <c r="AK22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM22" t="n">
         <v>13</v>
@@ -4424,7 +4491,7 @@
         <v>20</v>
       </c>
       <c r="AS22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT22" t="n">
         <v>6</v>
@@ -4445,7 +4512,7 @@
         <v>13</v>
       </c>
       <c r="AZ22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA22" t="n">
         <v>11</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -4483,55 +4550,55 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E23" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F23" t="n">
         <v>28</v>
       </c>
       <c r="G23" t="n">
-        <v>0.569</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H23" t="n">
         <v>48.4</v>
       </c>
       <c r="I23" t="n">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="J23" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L23" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="M23" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="N23" t="n">
         <v>0.377</v>
       </c>
       <c r="O23" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="P23" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.66</v>
+        <v>0.658</v>
       </c>
       <c r="R23" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S23" t="n">
         <v>31.3</v>
       </c>
       <c r="T23" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U23" t="n">
         <v>20.1</v>
@@ -4549,19 +4616,19 @@
         <v>4.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AE23" t="n">
         <v>11</v>
@@ -4582,7 +4649,7 @@
         <v>27</v>
       </c>
       <c r="AK23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4612,7 +4679,7 @@
         <v>12</v>
       </c>
       <c r="AU23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV23" t="n">
         <v>18</v>
@@ -4627,10 +4694,10 @@
         <v>2</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E24" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F24" t="n">
         <v>30</v>
       </c>
       <c r="G24" t="n">
-        <v>0.538</v>
+        <v>0.531</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
@@ -4683,10 +4750,10 @@
         <v>37.5</v>
       </c>
       <c r="J24" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.449</v>
+        <v>0.451</v>
       </c>
       <c r="L24" t="n">
         <v>5.3</v>
@@ -4695,7 +4762,7 @@
         <v>14.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
       <c r="O24" t="n">
         <v>13.5</v>
@@ -4707,13 +4774,13 @@
         <v>0.741</v>
       </c>
       <c r="R24" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S24" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T24" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U24" t="n">
         <v>22</v>
@@ -4722,19 +4789,19 @@
         <v>11.2</v>
       </c>
       <c r="W24" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X24" t="n">
         <v>5.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="AB24" t="n">
         <v>93.8</v>
@@ -4743,16 +4810,16 @@
         <v>4.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AE24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF24" t="n">
         <v>14</v>
       </c>
       <c r="AG24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH24" t="n">
         <v>23</v>
@@ -4764,7 +4831,7 @@
         <v>5</v>
       </c>
       <c r="AK24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL24" t="n">
         <v>24</v>
@@ -4785,13 +4852,13 @@
         <v>22</v>
       </c>
       <c r="AR24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS24" t="n">
         <v>6</v>
       </c>
       <c r="AT24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU24" t="n">
         <v>10</v>
@@ -4800,16 +4867,16 @@
         <v>1</v>
       </c>
       <c r="AW24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX24" t="n">
         <v>13</v>
       </c>
       <c r="AY24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -4847,49 +4914,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E25" t="n">
         <v>33</v>
       </c>
       <c r="F25" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5</v>
+        <v>0.508</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J25" t="n">
-        <v>82.5</v>
+        <v>82.3</v>
       </c>
       <c r="K25" t="n">
         <v>0.458</v>
       </c>
       <c r="L25" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M25" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="O25" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P25" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q25" t="n">
         <v>0.757</v>
       </c>
       <c r="R25" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S25" t="n">
         <v>30.8</v>
@@ -4898,13 +4965,13 @@
         <v>41.7</v>
       </c>
       <c r="U25" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="V25" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W25" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="X25" t="n">
         <v>5.5</v>
@@ -4919,7 +4986,7 @@
         <v>19.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>98.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="AC25" t="n">
         <v>-0.2</v>
@@ -4931,19 +4998,19 @@
         <v>17</v>
       </c>
       <c r="AF25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH25" t="n">
         <v>30</v>
       </c>
       <c r="AI25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK25" t="n">
         <v>6</v>
@@ -4955,13 +5022,13 @@
         <v>15</v>
       </c>
       <c r="AN25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO25" t="n">
         <v>19</v>
       </c>
       <c r="AP25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ25" t="n">
         <v>15</v>
@@ -4979,7 +5046,7 @@
         <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW25" t="n">
         <v>27</v>
@@ -4991,13 +5058,13 @@
         <v>4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA25" t="n">
         <v>15</v>
       </c>
       <c r="BB25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC25" t="n">
         <v>19</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>20</v>
@@ -5119,7 +5186,7 @@
         <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI26" t="n">
         <v>18</v>
@@ -5137,13 +5204,13 @@
         <v>8</v>
       </c>
       <c r="AN26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO26" t="n">
         <v>11</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ26" t="n">
         <v>2</v>
@@ -5170,13 +5237,13 @@
         <v>17</v>
       </c>
       <c r="AY26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB26" t="n">
         <v>16</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -5289,19 +5356,19 @@
         <v>-6</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
       </c>
       <c r="AF27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="n">
         <v>8</v>
@@ -5325,19 +5392,19 @@
         <v>12</v>
       </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR27" t="n">
         <v>2</v>
       </c>
       <c r="AS27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU27" t="n">
         <v>26</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E28" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.754</v>
+        <v>0.75</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
@@ -5411,7 +5478,7 @@
         <v>39.5</v>
       </c>
       <c r="J28" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="K28" t="n">
         <v>0.479</v>
@@ -5423,16 +5490,16 @@
         <v>21.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.395</v>
+        <v>0.396</v>
       </c>
       <c r="O28" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P28" t="n">
         <v>21.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.747</v>
+        <v>0.745</v>
       </c>
       <c r="R28" t="n">
         <v>10.2</v>
@@ -5450,28 +5517,28 @@
         <v>13.6</v>
       </c>
       <c r="W28" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y28" t="n">
         <v>5</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.6</v>
+        <v>103.5</v>
       </c>
       <c r="AC28" t="n">
         <v>7.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5519,7 +5586,7 @@
         <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AU28" t="n">
         <v>4</v>
@@ -5528,13 +5595,13 @@
         <v>3</v>
       </c>
       <c r="AW28" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AX28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-3.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE29" t="n">
         <v>24</v>
@@ -5665,7 +5732,7 @@
         <v>24</v>
       </c>
       <c r="AH29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI29" t="n">
         <v>29</v>
@@ -5686,16 +5753,16 @@
         <v>20</v>
       </c>
       <c r="AO29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ29" t="n">
         <v>12</v>
       </c>
       <c r="AR29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>0.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
         <v>14</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
@@ -5939,25 +6006,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F31" t="n">
         <v>46</v>
       </c>
       <c r="G31" t="n">
-        <v>0.292</v>
+        <v>0.281</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J31" t="n">
-        <v>83.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K31" t="n">
         <v>0.439</v>
@@ -5969,7 +6036,7 @@
         <v>16.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.318</v>
+        <v>0.319</v>
       </c>
       <c r="O31" t="n">
         <v>15.3</v>
@@ -5981,13 +6048,13 @@
         <v>0.729</v>
       </c>
       <c r="R31" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S31" t="n">
         <v>29.8</v>
       </c>
       <c r="T31" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U31" t="n">
         <v>19</v>
@@ -5996,13 +6063,13 @@
         <v>15.3</v>
       </c>
       <c r="W31" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X31" t="n">
         <v>6.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z31" t="n">
         <v>21.3</v>
@@ -6011,13 +6078,13 @@
         <v>18.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>93.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-5.4</v>
+        <v>-5.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6053,19 +6120,19 @@
         <v>27</v>
       </c>
       <c r="AP31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ31" t="n">
         <v>26</v>
       </c>
       <c r="AR31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU31" t="n">
         <v>27</v>
@@ -6080,7 +6147,7 @@
         <v>2</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ31" t="n">
         <v>26</v>
@@ -6092,7 +6159,7 @@
         <v>24</v>
       </c>
       <c r="BC31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-25-2011-12</t>
+          <t>2012-04-25</t>
         </is>
       </c>
     </row>
